--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.18132794545058</v>
+        <v>6.52946579113572</v>
       </c>
       <c r="D2" t="n">
-        <v>39.00905197451856</v>
+        <v>6.338970945859267</v>
       </c>
       <c r="E2" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F2" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.51886246726307</v>
+        <v>6.096815150930249</v>
       </c>
       <c r="D3" t="n">
-        <v>11.01135777277262</v>
+        <v>1.789345638075551</v>
       </c>
       <c r="E3" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F3" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.79624953480783</v>
+        <v>7.441890549406272</v>
       </c>
       <c r="D4" t="n">
-        <v>44.82557359809161</v>
+        <v>7.284155709689887</v>
       </c>
       <c r="E4" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F4" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.39940733537591</v>
+        <v>4.452403691998585</v>
       </c>
       <c r="D5" t="n">
-        <v>26.28099338552076</v>
+        <v>4.270661425147123</v>
       </c>
       <c r="E5" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F5" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.56402034121764</v>
+        <v>6.104153305447867</v>
       </c>
       <c r="D6" t="n">
-        <v>36.88442159133714</v>
+        <v>5.993718508592286</v>
       </c>
       <c r="E6" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F6" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.11754198710088</v>
+        <v>2.781600572903893</v>
       </c>
       <c r="D7" t="n">
-        <v>18.23115714124807</v>
+        <v>2.962563035452811</v>
       </c>
       <c r="E7" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F7" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.12920128265302</v>
+        <v>4.733495208431116</v>
       </c>
       <c r="D8" t="n">
-        <v>25.88793386166772</v>
+        <v>4.206789252521004</v>
       </c>
       <c r="E8" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F8" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.62917229574279</v>
+        <v>4.652240498058203</v>
       </c>
       <c r="D9" t="n">
-        <v>29.80691590545193</v>
+        <v>4.843623834635939</v>
       </c>
       <c r="E9" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F9" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.28997106809149</v>
+        <v>4.434620298564868</v>
       </c>
       <c r="D10" t="n">
-        <v>27.95408629008394</v>
+        <v>4.54253902213864</v>
       </c>
       <c r="E10" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F10" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.07045743751979</v>
+        <v>5.211449333596966</v>
       </c>
       <c r="D11" t="n">
-        <v>33.26712429508478</v>
+        <v>5.405907697951277</v>
       </c>
       <c r="E11" t="n">
-        <v>7.761482774353899</v>
+        <v>1.261240950832509</v>
       </c>
       <c r="F11" t="n">
-        <v>9.425427822711207</v>
+        <v>1.531632021190571</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
